--- a/Plantilla_Suficiencia.xlsx
+++ b/Plantilla_Suficiencia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brian\Downloads\Suficiencia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brian\AppData\Local\Temp\claude\c--Users-brian-Downloads-Suficiencia\bd96d883-1800-4952-ae8b-861fcb605b41\scratchpad\xl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C212B4-2572-47B9-A04A-D008552C05A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216A4612-BB95-4A94-80C8-7C9A2496F201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2820" yWindow="2820" windowWidth="17280" windowHeight="8964" xr2:uid="{7C6F3926-99F4-41DF-8C6C-18892B538A9E}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8964" xr2:uid="{D8BB231B-82E5-4F79-B515-71EEA7B38696}"/>
   </bookViews>
   <sheets>
     <sheet name="Guia" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="293">
   <si>
     <t>Parámetros (ajustes generales)</t>
   </si>
@@ -104,10 +104,10 @@
     <t>Si una iniciativa aporta menos de este % de la brecha (o su ejecución es 0 %), se marca REEMPLAZAR.</t>
   </si>
   <si>
-    <t>Peso mínimo para SIN COBERTURA</t>
-  </si>
-  <si>
-    <t>Un dolor cuya atribución es mayor a este valor...</t>
+    <t>Impacto mínimo para SIN COBERTURA</t>
+  </si>
+  <si>
+    <t>Un dolor cuyo impacto es mayor a este valor...</t>
   </si>
   <si>
     <t>Resolución mínima para SIN COBERTURA</t>
@@ -197,7 +197,7 @@
     <t>Distancia entre hoy y la meta 2027. Es lo que las iniciativas deben recuperar.</t>
   </si>
   <si>
-    <t>Ej.: clientes que se dieron de baja en el periodo. Sirve para calcular la prevalencia.</t>
+    <t>Ej.: clientes que se dieron de baja en el periodo. Sirve para calcular el % dolor.</t>
   </si>
   <si>
     <t>PASO 2 · ¿Qué causa el problema?  (dolores = porciones del pastel)</t>
@@ -224,16 +224,16 @@
     <t>Dolor 6</t>
   </si>
   <si>
-    <t>% Atribución usada</t>
-  </si>
-  <si>
-    <t>% Atribución manual  (opcional)</t>
-  </si>
-  <si>
-    <t>% Atribución automática  (su parte del pastel)</t>
-  </si>
-  <si>
-    <t>% Prevalencia  (casos ÷ total analizado)</t>
+    <t>Impacto del dolor · usado</t>
+  </si>
+  <si>
+    <t>Impacto del dolor · manual  (opcional)</t>
+  </si>
+  <si>
+    <t>Impacto del dolor · automático  (su porción del pastel)</t>
+  </si>
+  <si>
+    <t>% dolor  (casos ÷ total analizado)</t>
   </si>
   <si>
     <t>Casos con este dolor</t>
@@ -341,6 +341,9 @@
     <t>% del dolor resuelto · Plan</t>
   </si>
   <si>
+    <t>Impacto del dolor</t>
+  </si>
+  <si>
     <t>Alerta</t>
   </si>
   <si>
@@ -701,7 +704,7 @@
     <t>PASO 2 · ¿Qué lo causa?</t>
   </si>
   <si>
-    <t>Escribe los dolores y cuántos casos tiene cada uno. La plantilla calcula su peso en el pastel.</t>
+    <t>Escribe los dolores y cuántos casos tiene cada uno. La plantilla calcula su % dolor y su impacto (su porción del pastel).</t>
   </si>
   <si>
     <t>PASO 3 · ¿Qué voy a hacer?</t>
@@ -764,9 +767,6 @@
     <t>Dolor</t>
   </si>
   <si>
-    <t>Atribución (peso)</t>
-  </si>
-  <si>
     <t>X resuelve</t>
   </si>
   <si>
@@ -839,16 +839,13 @@
     <t>Una causa del problema, sacada del análisis de datos del indicador.</t>
   </si>
   <si>
-    <t>Prevalencia</t>
+    <t>% dolor</t>
   </si>
   <si>
     <t>% de casos que tienen ese dolor. La suma puede pasar de 100 % (un caso puede tener varios dolores).</t>
   </si>
   <si>
-    <t>Atribución</t>
-  </si>
-  <si>
-    <t>Parte del pastel que le toca a cada dolor. Siempre suma 100 %.</t>
+    <t>Qué parte del problema total explica cada dolor: el tamaño de su porción del pastel. Siempre suma 100 %.</t>
   </si>
   <si>
     <t>Efectividad</t>
@@ -926,10 +923,10 @@
     <t>• En el Paso 1 escribe solo números (2,8 y no 2,8 %). En los Pasos 2 y 3 los porcentajes sí llevan % (40 %).</t>
   </si>
   <si>
-    <t>• Si cambias una atribución a mano, cámbialas todas para que sumen 100 %.</t>
-  </si>
-  <si>
-    <t>• Máximo 6 dolores y 8 iniciativas por indicador (cabe en una pantalla).</t>
+    <t>• Si cambias un impacto a mano, cámbialos todos para que sumen 100 %.</t>
+  </si>
+  <si>
+    <t>• Máximo 6 dolores y 8 iniciativas por indicador. Si necesitas más (hasta 15), usa la calculadora web (suficiencia_cx.html) y exporta a Excel.</t>
   </si>
   <si>
     <t>• Las hojas están protegidas sin contraseña para cuidar las fórmulas: Revisar &gt; Desproteger hoja.</t>
@@ -939,11 +936,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.000000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.000000"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -1200,7 +1196,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1228,10 +1224,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2451,7 +2447,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-30C3-4CF2-BA90-67564042D5F0}"/>
+              <c16:uniqueId val="{00000001-7442-4E17-A178-A6E2C6E7F66F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2520,7 +2516,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-30C3-4CF2-BA90-67564042D5F0}"/>
+              <c16:uniqueId val="{00000002-7442-4E17-A178-A6E2C6E7F66F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2533,8 +2529,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="1217615424"/>
-        <c:axId val="1217615904"/>
+        <c:axId val="1374262591"/>
+        <c:axId val="1372002191"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2588,7 +2584,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-30C3-4CF2-BA90-67564042D5F0}"/>
+              <c16:uniqueId val="{00000003-7442-4E17-A178-A6E2C6E7F66F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2602,11 +2598,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="1217615424"/>
-        <c:axId val="1217615904"/>
+        <c:axId val="1374262591"/>
+        <c:axId val="1372002191"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1217615424"/>
+        <c:axId val="1374262591"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2616,7 +2612,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1217615904"/>
+        <c:crossAx val="1372002191"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2624,7 +2620,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1217615904"/>
+        <c:axId val="1372002191"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2636,7 +2632,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1217615424"/>
+        <c:crossAx val="1374262591"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2718,7 +2714,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000002-9281-4B5E-9BB7-5EEEC47CD994}"/>
+                <c16:uniqueId val="{00000002-2AEF-4A10-BF18-CCD04926E66E}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2733,7 +2729,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-9281-4B5E-9BB7-5EEEC47CD994}"/>
+                <c16:uniqueId val="{00000003-2AEF-4A10-BF18-CCD04926E66E}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2748,7 +2744,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000004-9281-4B5E-9BB7-5EEEC47CD994}"/>
+                <c16:uniqueId val="{00000004-2AEF-4A10-BF18-CCD04926E66E}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2763,7 +2759,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-9281-4B5E-9BB7-5EEEC47CD994}"/>
+                <c16:uniqueId val="{00000005-2AEF-4A10-BF18-CCD04926E66E}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2832,7 +2828,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-9281-4B5E-9BB7-5EEEC47CD994}"/>
+              <c16:uniqueId val="{00000001-2AEF-4A10-BF18-CCD04926E66E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2845,11 +2841,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="1211331136"/>
-        <c:axId val="1217089920"/>
+        <c:axId val="1374265951"/>
+        <c:axId val="1374265471"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1211331136"/>
+        <c:axId val="1374265951"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2859,7 +2855,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1217089920"/>
+        <c:crossAx val="1374265471"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2867,7 +2863,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1217089920"/>
+        <c:axId val="1374265471"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2878,7 +2874,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1211331136"/>
+        <c:crossAx val="1374265951"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2956,7 +2952,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000002-BAE2-468D-AFC5-7A4462B4C5D7}"/>
+                <c16:uniqueId val="{00000002-22E5-4696-A515-13BAC9DF8144}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2971,7 +2967,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-BAE2-468D-AFC5-7A4462B4C5D7}"/>
+                <c16:uniqueId val="{00000003-22E5-4696-A515-13BAC9DF8144}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2986,7 +2982,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000004-BAE2-468D-AFC5-7A4462B4C5D7}"/>
+                <c16:uniqueId val="{00000004-22E5-4696-A515-13BAC9DF8144}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3001,7 +2997,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-BAE2-468D-AFC5-7A4462B4C5D7}"/>
+                <c16:uniqueId val="{00000005-22E5-4696-A515-13BAC9DF8144}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3070,7 +3066,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-BAE2-468D-AFC5-7A4462B4C5D7}"/>
+              <c16:uniqueId val="{00000001-22E5-4696-A515-13BAC9DF8144}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3083,11 +3079,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="1217090880"/>
-        <c:axId val="1217091360"/>
+        <c:axId val="1374261151"/>
+        <c:axId val="1374261631"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1217090880"/>
+        <c:axId val="1374261151"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3097,7 +3093,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1217091360"/>
+        <c:crossAx val="1374261631"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3105,7 +3101,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1217091360"/>
+        <c:axId val="1374261631"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3116,7 +3112,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1217090880"/>
+        <c:crossAx val="1374261151"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3194,7 +3190,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000002-5D13-4FDC-8886-6BFB94827664}"/>
+                <c16:uniqueId val="{00000002-3552-44DB-A8EA-BFCDC057A822}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3209,7 +3205,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-5D13-4FDC-8886-6BFB94827664}"/>
+                <c16:uniqueId val="{00000003-3552-44DB-A8EA-BFCDC057A822}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3224,7 +3220,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000004-5D13-4FDC-8886-6BFB94827664}"/>
+                <c16:uniqueId val="{00000004-3552-44DB-A8EA-BFCDC057A822}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3239,7 +3235,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-5D13-4FDC-8886-6BFB94827664}"/>
+                <c16:uniqueId val="{00000005-3552-44DB-A8EA-BFCDC057A822}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3308,7 +3304,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-5D13-4FDC-8886-6BFB94827664}"/>
+              <c16:uniqueId val="{00000001-3552-44DB-A8EA-BFCDC057A822}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3321,11 +3317,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="1217618304"/>
-        <c:axId val="1217614944"/>
+        <c:axId val="1374264511"/>
+        <c:axId val="1374267391"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1217618304"/>
+        <c:axId val="1374264511"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3335,7 +3331,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1217614944"/>
+        <c:crossAx val="1374267391"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3343,7 +3339,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1217614944"/>
+        <c:axId val="1374267391"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3354,7 +3350,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1217618304"/>
+        <c:crossAx val="1374264511"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3398,7 +3394,7 @@
         <xdr:cNvPr id="2" name="Gráfico 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C09777BD-3853-F961-C003-7F88F8AC376E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC781A2C-9403-F5FC-D333-B6EA91705C03}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3439,7 +3435,7 @@
         <xdr:cNvPr id="2" name="Gráfico 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18556E88-3CB0-DE28-F626-30FE1DFD526D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51EAC4EA-65B3-CFC4-26B3-533A3D5509BE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3480,7 +3476,7 @@
         <xdr:cNvPr id="2" name="Gráfico 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D798E21A-4FE5-6858-A2A6-9DA861456615}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3428F2A6-C5A8-A597-10A4-0DF0BAEE9D69}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3521,7 +3517,7 @@
         <xdr:cNvPr id="2" name="Gráfico 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB8DA3CC-0E46-A43D-A266-5D4FB6E3555F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B23E10A-CD1C-CCB6-406F-7ABBFAD3D805}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3838,7 +3834,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DCFA2A9-AF50-42DB-ABF4-2A2AEC3B309C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D90F960E-5C02-4075-9150-A5B41C94F66F}">
   <sheetPr>
     <tabColor rgb="FF008000"/>
   </sheetPr>
@@ -3853,17 +3849,17 @@
   <sheetData>
     <row r="1" spans="1:10" ht="22.8" x14ac:dyDescent="0.25">
       <c r="A1" s="43" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -3877,37 +3873,37 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" s="12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -3921,39 +3917,39 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" s="12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" s="12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -3967,39 +3963,39 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B19" s="44" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B20" s="45" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B21" s="46" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B22" s="47" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -4013,29 +4009,29 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B25" s="12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C25" s="13">
         <v>10</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B26" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C26" s="13">
         <v>4</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B27" s="12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C27" s="26">
         <v>1</v>
@@ -4043,7 +4039,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B28" s="12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C28" s="26">
         <v>0.5</v>
@@ -4051,10 +4047,10 @@
     </row>
     <row r="30" spans="1:10" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>237</v>
+        <v>96</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>238</v>
@@ -4267,7 +4263,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B51" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>260</v>
@@ -4275,7 +4271,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B52" s="12" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>261</v>
@@ -4291,47 +4287,47 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B54" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C54" s="7" t="s">
         <v>264</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B55" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C55" s="7" t="s">
         <v>266</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B56" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="C56" s="7" t="s">
         <v>268</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B57" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="C57" s="7" t="s">
         <v>270</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B58" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="C58" s="7" t="s">
         <v>272</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -4345,47 +4341,47 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B61" s="25" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B62" s="25" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B63" s="25" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B64" s="25" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B65" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="C65" s="7" t="s">
         <v>279</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -4399,31 +4395,31 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B68" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="C68" s="7" t="s">
         <v>282</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B69" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C69" s="7" t="s">
         <v>284</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B70" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="C70" s="7" t="s">
         <v>286</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -4437,27 +4433,27 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B73" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B74" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B75" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B76" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B77" s="7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -4501,11 +4497,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{286A130F-F82E-477F-A7E2-DA4806CED555}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{652C8612-45A6-4641-9BD3-AD6FAE7375A0}">
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:XFD52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="7" customWidth="1"/>
@@ -4522,24 +4518,25 @@
     <col min="18" max="16384" width="11.5546875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17 16384:16384" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+      <c r="XFD1"/>
+    </row>
+    <row r="2" spans="1:17 16384:16384" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17 16384:16384" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17 16384:16384" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -4558,65 +4555,65 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
     </row>
-    <row r="5" spans="1:17" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17 16384:16384" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>66</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>40</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K5" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M5" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>186</v>
       </c>
       <c r="N5" s="4" t="s">
         <v>88</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17 16384:16384" x14ac:dyDescent="0.25">
       <c r="A6" s="25">
         <v>1</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C6" s="14" t="str">
         <f t="shared" ref="C6:C15" ca="1" si="0">IF($B6="","",IFERROR(INDIRECT("'"&amp;$B6&amp;"'!C5"),"⚠ Hoja no encontrada"))</f>
@@ -4679,12 +4676,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17 16384:16384" x14ac:dyDescent="0.25">
       <c r="A7" s="25">
         <v>2</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C7" s="14" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -4747,7 +4744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17 16384:16384" x14ac:dyDescent="0.25">
       <c r="A8" s="25">
         <v>3</v>
       </c>
@@ -4813,7 +4810,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17 16384:16384" x14ac:dyDescent="0.25">
       <c r="A9" s="25">
         <v>4</v>
       </c>
@@ -4879,7 +4876,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17 16384:16384" x14ac:dyDescent="0.25">
       <c r="A10" s="25">
         <v>5</v>
       </c>
@@ -4945,7 +4942,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17 16384:16384" x14ac:dyDescent="0.25">
       <c r="A11" s="25">
         <v>6</v>
       </c>
@@ -5011,7 +5008,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17 16384:16384" x14ac:dyDescent="0.25">
       <c r="A12" s="25">
         <v>7</v>
       </c>
@@ -5077,7 +5074,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17 16384:16384" x14ac:dyDescent="0.25">
       <c r="A13" s="25">
         <v>8</v>
       </c>
@@ -5143,7 +5140,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17 16384:16384" x14ac:dyDescent="0.25">
       <c r="A14" s="25">
         <v>9</v>
       </c>
@@ -5209,7 +5206,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17 16384:16384" x14ac:dyDescent="0.25">
       <c r="A15" s="25">
         <v>10</v>
       </c>
@@ -5277,7 +5274,7 @@
     </row>
     <row r="17" spans="1:17" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -5298,7 +5295,7 @@
     </row>
     <row r="36" spans="1:17" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -5319,10 +5316,10 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B37" s="42" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D37" s="12" t="str">
         <f ca="1">IF(C37="","",IFERROR(INDIRECT("'"&amp;C37&amp;"'!C5"),"⚠ Hoja no encontrada"))</f>
@@ -5331,22 +5328,22 @@
     </row>
     <row r="38" spans="1:17" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>67</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>87</v>
@@ -5586,7 +5583,7 @@
     </row>
     <row r="48" spans="1:17" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -5607,34 +5604,34 @@
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="25" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="25" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="25" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="25" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -5700,7 +5697,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C37" xr:uid="{55BBB18B-6238-4F21-83C5-E826489EAC2D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C37" xr:uid="{D9E015BB-DAFC-4F0C-AEE5-47FA42AE1E3A}">
       <formula1>$B$6:$B$15</formula1>
     </dataValidation>
   </dataValidations>
@@ -5710,7 +5707,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F74F6CC2-414F-4F0E-8B7B-28B9C695B6AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACC8EB99-5440-4274-8A4E-35B0CA97536A}">
   <sheetPr>
     <tabColor rgb="FF5B9BD5"/>
   </sheetPr>
@@ -5781,7 +5778,7 @@
         <v>41</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>42</v>
@@ -5804,7 +5801,7 @@
         <v>40</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>43</v>
@@ -5943,19 +5940,19 @@
         <v>62</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H17" s="19"/>
     </row>
@@ -6083,19 +6080,19 @@
         <v>64</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H23" s="19"/>
     </row>
@@ -6104,14 +6101,14 @@
         <v>63</v>
       </c>
       <c r="C24" s="7" t="str">
-        <f>IF(SUM(C22:H22)=0,"⚠ Aún no hay dolores con casos.",IF(ABS(SUM(C22:H22)-1)&lt;0.0005,"✔ La atribución suma 100 %.","⚠ La atribución suma "&amp;FIXED(SUM(C22:H22)*100,1)&amp;" %; debe sumar 100 %. Revisa la fila 21."))</f>
-        <v>✔ La atribución suma 100 %.</v>
+        <f>IF(SUM(C22:H22)=0,"⚠ Aún no hay dolores con casos.",IF(ABS(SUM(C22:H22)-1)&lt;0.0005,"✔ El impacto de los dolores suma 100 %.","⚠ El impacto de los dolores suma "&amp;FIXED(SUM(C22:H22)*100,1)&amp;" %; debe sumar 100 %. Revisa la fila 21."))</f>
+        <v>✔ El impacto de los dolores suma 100 %.</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C25" s="11" t="str">
-        <f>"La suma de prevalencias es "&amp;FIXED(SUM(C19:H19)*100,0)&amp;" %. Puede pasar de 100 % porque un caso puede tener varios dolores. Es normal."</f>
-        <v>La suma de prevalencias es 130 %. Puede pasar de 100 % porque un caso puede tener varios dolores. Es normal.</v>
+        <f>"Los % dolor suman "&amp;FIXED(SUM(C19:H19)*100,0)&amp;" %. Puede pasar de 100 % porque un caso puede tener varios dolores. Es normal."</f>
+        <v>Los % dolor suman 130 %. Puede pasar de 100 % porque un caso puede tener varios dolores. Es normal.</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -6187,7 +6184,7 @@
         <v>72</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C29" s="27">
         <v>0.45</v>
@@ -6204,13 +6201,13 @@
         <v>30</v>
       </c>
       <c r="K29" s="28" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L29" s="29">
         <v>46477</v>
       </c>
       <c r="M29" s="19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N29" s="14" t="str">
         <f t="shared" ref="N29:N36" si="6">IF(B29="","",IF(I29="","⚠ Falta % de ejecución",IF(M29="","⚠ Sin respaldo","✔ OK")))</f>
@@ -6222,7 +6219,7 @@
         <v>73</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C30" s="27">
         <v>0.1</v>
@@ -6241,13 +6238,13 @@
         <v>28</v>
       </c>
       <c r="K30" s="28" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L30" s="29">
         <v>46371</v>
       </c>
       <c r="M30" s="19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N30" s="14" t="str">
         <f t="shared" si="6"/>
@@ -6259,7 +6256,7 @@
         <v>74</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C31" s="27"/>
       <c r="D31" s="27">
@@ -6276,13 +6273,13 @@
         <v>29</v>
       </c>
       <c r="K31" s="28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L31" s="29">
         <v>46568</v>
       </c>
       <c r="M31" s="19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N31" s="14" t="str">
         <f t="shared" si="6"/>
@@ -6294,7 +6291,7 @@
         <v>75</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C32" s="27"/>
       <c r="D32" s="27"/>
@@ -6313,13 +6310,13 @@
         <v>28</v>
       </c>
       <c r="K32" s="28" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L32" s="29">
         <v>46418</v>
       </c>
       <c r="M32" s="19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N32" s="14" t="str">
         <f t="shared" si="6"/>
@@ -6331,7 +6328,7 @@
         <v>76</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C33" s="27">
         <v>0.01</v>
@@ -6348,7 +6345,7 @@
         <v>28</v>
       </c>
       <c r="K33" s="28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L33" s="29">
         <v>46356</v>
@@ -6586,7 +6583,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B50" s="12" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="C50" s="34">
         <f t="shared" ref="C50:H50" si="11">C22</f>
@@ -6731,7 +6728,7 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B55" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C55" s="35" t="str">
         <f>IF(C17="","",IF(AND(C50&gt;Cobertura_Atrib_Min,C52&lt;Cobertura_Resuelto_Min),"⚠ SIN COBERTURA",IF(C52&gt;=Cobertura_Resuelto_Min,"✔ Cubierto","○ Peso bajo")))</f>
@@ -6763,19 +6760,19 @@
         <v>66</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>87</v>
@@ -7022,22 +7019,22 @@
     </row>
     <row r="67" spans="1:14" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C67" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="D67" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="E67" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="F67" s="37" t="s">
         <v>102</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C67" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="D67" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="E67" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="F67" s="37" t="s">
-        <v>101</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>87</v>
@@ -7277,7 +7274,7 @@
     </row>
     <row r="77" spans="1:14" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -7296,7 +7293,7 @@
     <row r="79" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4"/>
       <c r="B79" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C79" s="4" t="str">
         <f t="shared" ref="C79:H79" si="22">IF(C$17="","Dolor "&amp;(COLUMN()-2),C$17)</f>
@@ -7589,7 +7586,7 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B88" s="20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C88" s="30">
         <f t="shared" ref="C88:H88" si="24">PRODUCT(C80:C87)</f>
@@ -7618,7 +7615,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B89" s="20" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C89" s="30">
         <f t="shared" ref="C89:H89" si="25">1-C88</f>
@@ -7648,7 +7645,7 @@
     <row r="91" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="4"/>
       <c r="B91" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C91" s="4" t="str">
         <f t="shared" ref="C91:H91" si="26">IF(C$17="","Dolor "&amp;(COLUMN()-2),C$17)</f>
@@ -7941,7 +7938,7 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B100" s="20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C100" s="30">
         <f t="shared" ref="C100:H100" si="28">PRODUCT(C92:C99)</f>
@@ -7970,7 +7967,7 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B101" s="20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C101" s="30">
         <f t="shared" ref="C101:H101" si="29">1-C100</f>
@@ -8000,7 +7997,7 @@
     <row r="103" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="4"/>
       <c r="B103" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C103" s="4" t="str">
         <f t="shared" ref="C103:H103" si="30">IF(C$17="","Dolor "&amp;(COLUMN()-2),C$17)</f>
@@ -8027,19 +8024,19 @@
         <v>Dolor 6</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L103" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M103" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
@@ -8468,13 +8465,13 @@
     </row>
     <row r="113" spans="1:3" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -8551,7 +8548,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B123" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>14</v>
@@ -8559,7 +8556,7 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B124" s="14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C124" s="16">
         <f>N(C8)</f>
@@ -8568,7 +8565,7 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B125" s="14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C125" s="16">
         <f>N(D44)</f>
@@ -8577,7 +8574,7 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B126" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C126" s="16">
         <f>N(C44)</f>
@@ -8595,7 +8592,7 @@
     </row>
     <row r="129" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B129" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>14</v>
@@ -8603,7 +8600,7 @@
     </row>
     <row r="130" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B130" s="14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C130" s="14" t="str">
         <f>IF(C7="%","pp",IF(C7="","puntos",C7))</f>
@@ -8612,7 +8609,7 @@
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B131" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C131" s="14">
         <f>IF(C10="",IF(C6="Sube es mejor",100,0),C10)</f>
@@ -8621,7 +8618,7 @@
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B132" s="14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C132" s="14">
         <f>IF(MAX(C22:H22)=0,0,MATCH(MAX(C22:H22),C22:H22,0))</f>
@@ -8630,7 +8627,7 @@
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B133" s="14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C133" s="14" t="str">
         <f>IF(C132=0,"",INDEX(C17:H17,C132))</f>
@@ -8716,17 +8713,17 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Casos" error="Escribe un número entero mayor o igual a 0." sqref="C13" xr:uid="{459DF58A-0F1F-4AF9-8918-1325C4F468B3}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Casos" error="Escribe un número entero mayor o igual a 0." sqref="C13" xr:uid="{D2D7B349-034A-43CE-BA4F-D68F3343B042}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Casos" error="Escribe un número entero mayor o igual a 0." sqref="C18:H18" xr:uid="{23ABA0AE-C6A5-4F99-925D-47D65AD89F0D}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Casos" error="Escribe un número entero mayor o igual a 0." sqref="C18:H18" xr:uid="{E3417E0E-7F40-4F6D-AE26-2ADF4F8A7B01}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Porcentaje" error="Escribe un porcentaje entre 0 % y 100 % (ej. 40 %)." sqref="C21:H21" xr:uid="{17CB03CC-AAAC-469C-9E18-E5604122C97E}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Porcentaje" error="Escribe un porcentaje entre 0 % y 100 % (ej. 40 %)." sqref="C21:H21" xr:uid="{24C00579-B36B-4D82-BC57-64EFF7130917}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Porcentaje" error="Escribe un porcentaje entre 0 % y 100 % (ej. 40 %)." sqref="C29:I36" xr:uid="{1491037D-400E-4172-A117-7B524B9FA39C}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Porcentaje" error="Escribe un porcentaje entre 0 % y 100 % (ej. 40 %)." sqref="C29:I36" xr:uid="{C49B5201-11BB-4141-8666-62AD4970801D}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -8736,13 +8733,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{896BAE57-167E-462D-B266-F7E691641D95}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E7094B93-3FD6-4D6A-8B6A-10927FB3F407}">
           <x14:formula1>
             <xm:f>Parametros!$B$19:$B$20</xm:f>
           </x14:formula1>
           <xm:sqref>C6</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{67EFC7F4-FD1F-4BE3-9B9F-A7ADE3E55A77}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{45130CDC-9290-48B7-A684-3025CFD8EBA3}">
           <x14:formula1>
             <xm:f>Parametros!$C$19:$C$21</xm:f>
           </x14:formula1>
@@ -8755,7 +8752,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{927042BF-7369-4099-BF26-2E714A405C72}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A37C8E3-11A9-4A90-99D5-A1BFBAE1721C}">
   <sheetPr>
     <tabColor rgb="FF5B9BD5"/>
   </sheetPr>
@@ -8826,7 +8823,7 @@
         <v>41</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>42</v>
@@ -8849,7 +8846,7 @@
         <v>40</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>43</v>
@@ -8988,16 +8985,16 @@
         <v>62</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G17" s="19"/>
       <c r="H17" s="19"/>
@@ -9124,16 +9121,16 @@
         <v>64</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G23" s="19"/>
       <c r="H23" s="19"/>
@@ -9143,14 +9140,14 @@
         <v>63</v>
       </c>
       <c r="C24" s="7" t="str">
-        <f>IF(SUM(C22:H22)=0,"⚠ Aún no hay dolores con casos.",IF(ABS(SUM(C22:H22)-1)&lt;0.0005,"✔ La atribución suma 100 %.","⚠ La atribución suma "&amp;FIXED(SUM(C22:H22)*100,1)&amp;" %; debe sumar 100 %. Revisa la fila 21."))</f>
-        <v>✔ La atribución suma 100 %.</v>
+        <f>IF(SUM(C22:H22)=0,"⚠ Aún no hay dolores con casos.",IF(ABS(SUM(C22:H22)-1)&lt;0.0005,"✔ El impacto de los dolores suma 100 %.","⚠ El impacto de los dolores suma "&amp;FIXED(SUM(C22:H22)*100,1)&amp;" %; debe sumar 100 %. Revisa la fila 21."))</f>
+        <v>✔ El impacto de los dolores suma 100 %.</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C25" s="11" t="str">
-        <f>"La suma de prevalencias es "&amp;FIXED(SUM(C19:H19)*100,0)&amp;" %. Puede pasar de 100 % porque un caso puede tener varios dolores. Es normal."</f>
-        <v>La suma de prevalencias es 110 %. Puede pasar de 100 % porque un caso puede tener varios dolores. Es normal.</v>
+        <f>"Los % dolor suman "&amp;FIXED(SUM(C19:H19)*100,0)&amp;" %. Puede pasar de 100 % porque un caso puede tener varios dolores. Es normal."</f>
+        <v>Los % dolor suman 110 %. Puede pasar de 100 % porque un caso puede tener varios dolores. Es normal.</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -9226,7 +9223,7 @@
         <v>72</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C29" s="27"/>
       <c r="D29" s="27">
@@ -9243,13 +9240,13 @@
         <v>28</v>
       </c>
       <c r="K29" s="28" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L29" s="29">
         <v>46387</v>
       </c>
       <c r="M29" s="19" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N29" s="14" t="str">
         <f t="shared" ref="N29:N36" si="6">IF(B29="","",IF(I29="","⚠ Falta % de ejecución",IF(M29="","⚠ Sin respaldo","✔ OK")))</f>
@@ -9261,7 +9258,7 @@
         <v>73</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C30" s="27">
         <v>0.6</v>
@@ -9278,13 +9275,13 @@
         <v>29</v>
       </c>
       <c r="K30" s="28" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L30" s="29">
         <v>46446</v>
       </c>
       <c r="M30" s="19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N30" s="14" t="str">
         <f t="shared" si="6"/>
@@ -9296,7 +9293,7 @@
         <v>74</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C31" s="27">
         <v>0.1</v>
@@ -9315,13 +9312,13 @@
         <v>28</v>
       </c>
       <c r="K31" s="28" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L31" s="29">
         <v>46402</v>
       </c>
       <c r="M31" s="19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N31" s="14" t="str">
         <f t="shared" si="6"/>
@@ -9333,7 +9330,7 @@
         <v>75</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C32" s="27"/>
       <c r="D32" s="27">
@@ -9352,13 +9349,13 @@
         <v>28</v>
       </c>
       <c r="K32" s="28" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L32" s="29">
         <v>46477</v>
       </c>
       <c r="M32" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N32" s="14" t="str">
         <f t="shared" si="6"/>
@@ -9613,7 +9610,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B50" s="12" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="C50" s="34">
         <f t="shared" ref="C50:H50" si="11">C22</f>
@@ -9758,7 +9755,7 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B55" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C55" s="35" t="str">
         <f>IF(C17="","",IF(AND(C50&gt;Cobertura_Atrib_Min,C52&lt;Cobertura_Resuelto_Min),"⚠ SIN COBERTURA",IF(C52&gt;=Cobertura_Resuelto_Min,"✔ Cubierto","○ Peso bajo")))</f>
@@ -9790,19 +9787,19 @@
         <v>66</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>87</v>
@@ -10049,22 +10046,22 @@
     </row>
     <row r="67" spans="1:14" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C67" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="D67" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="E67" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="F67" s="37" t="s">
         <v>102</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C67" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="D67" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="E67" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="F67" s="37" t="s">
-        <v>101</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>87</v>
@@ -10304,7 +10301,7 @@
     </row>
     <row r="77" spans="1:14" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -10323,7 +10320,7 @@
     <row r="79" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4"/>
       <c r="B79" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C79" s="4" t="str">
         <f t="shared" ref="C79:H79" si="22">IF(C$17="","Dolor "&amp;(COLUMN()-2),C$17)</f>
@@ -10616,7 +10613,7 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B88" s="20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C88" s="30">
         <f t="shared" ref="C88:H88" si="24">PRODUCT(C80:C87)</f>
@@ -10645,7 +10642,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B89" s="20" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C89" s="30">
         <f t="shared" ref="C89:H89" si="25">1-C88</f>
@@ -10675,7 +10672,7 @@
     <row r="91" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="4"/>
       <c r="B91" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C91" s="4" t="str">
         <f t="shared" ref="C91:H91" si="26">IF(C$17="","Dolor "&amp;(COLUMN()-2),C$17)</f>
@@ -10968,7 +10965,7 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B100" s="20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C100" s="30">
         <f t="shared" ref="C100:H100" si="28">PRODUCT(C92:C99)</f>
@@ -10997,7 +10994,7 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B101" s="20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C101" s="30">
         <f t="shared" ref="C101:H101" si="29">1-C100</f>
@@ -11027,7 +11024,7 @@
     <row r="103" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="4"/>
       <c r="B103" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C103" s="4" t="str">
         <f t="shared" ref="C103:H103" si="30">IF(C$17="","Dolor "&amp;(COLUMN()-2),C$17)</f>
@@ -11054,19 +11051,19 @@
         <v>Dolor 6</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L103" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M103" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
@@ -11495,13 +11492,13 @@
     </row>
     <row r="113" spans="1:3" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -11578,7 +11575,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B123" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>14</v>
@@ -11586,7 +11583,7 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B124" s="14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C124" s="16">
         <f>N(C8)</f>
@@ -11595,7 +11592,7 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B125" s="14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C125" s="16">
         <f>N(D44)</f>
@@ -11604,7 +11601,7 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B126" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C126" s="16">
         <f>N(C44)</f>
@@ -11622,7 +11619,7 @@
     </row>
     <row r="129" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B129" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>14</v>
@@ -11630,7 +11627,7 @@
     </row>
     <row r="130" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B130" s="14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C130" s="14" t="str">
         <f>IF(C7="%","pp",IF(C7="","puntos",C7))</f>
@@ -11639,7 +11636,7 @@
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B131" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C131" s="14">
         <f>IF(C10="",IF(C6="Sube es mejor",100,0),C10)</f>
@@ -11648,7 +11645,7 @@
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B132" s="14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C132" s="14">
         <f>IF(MAX(C22:H22)=0,0,MATCH(MAX(C22:H22),C22:H22,0))</f>
@@ -11657,7 +11654,7 @@
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B133" s="14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C133" s="14" t="str">
         <f>IF(C132=0,"",INDEX(C17:H17,C132))</f>
@@ -11743,17 +11740,17 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Casos" error="Escribe un número entero mayor o igual a 0." sqref="C13" xr:uid="{4FE71D7C-378D-4DF1-ABDF-BEA5B28EB240}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Casos" error="Escribe un número entero mayor o igual a 0." sqref="C13" xr:uid="{D220B288-AB50-4395-9773-62E11CF84C90}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Casos" error="Escribe un número entero mayor o igual a 0." sqref="C18:H18" xr:uid="{5563DD7F-382D-4D21-B964-CDDE000556D1}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Casos" error="Escribe un número entero mayor o igual a 0." sqref="C18:H18" xr:uid="{7DA60797-68BB-45CA-B710-73AC81C66662}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Porcentaje" error="Escribe un porcentaje entre 0 % y 100 % (ej. 40 %)." sqref="C21:H21" xr:uid="{B62527EE-4CAA-4888-96F7-F1338222F97E}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Porcentaje" error="Escribe un porcentaje entre 0 % y 100 % (ej. 40 %)." sqref="C21:H21" xr:uid="{3CA33722-655A-4D47-9671-A4D900FB09E6}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Porcentaje" error="Escribe un porcentaje entre 0 % y 100 % (ej. 40 %)." sqref="C29:I36" xr:uid="{90EA22FA-1961-4C04-BD5C-22C3FF98BBB0}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Porcentaje" error="Escribe un porcentaje entre 0 % y 100 % (ej. 40 %)." sqref="C29:I36" xr:uid="{08B1B9F4-169B-4168-9D93-017AC8FB7363}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -11763,13 +11760,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8AAA92D8-88EE-4C2A-9A94-E95B4995771A}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1673DE66-9DE9-4DA5-BF43-672E48FE2DD0}">
           <x14:formula1>
             <xm:f>Parametros!$B$19:$B$20</xm:f>
           </x14:formula1>
           <xm:sqref>C6</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CAB61DF7-7566-46D8-8871-7D198E531536}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B6F84FEE-0EAA-4C1D-883A-2BAB523428D2}">
           <x14:formula1>
             <xm:f>Parametros!$C$19:$C$21</xm:f>
           </x14:formula1>
@@ -11782,7 +11779,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{627DFB8B-1C05-43F2-8EAE-12262DAFCDA4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21B0D5D2-9A65-4842-8C7A-AF0CB05AE6A4}">
   <sheetPr>
     <tabColor rgb="FFA6A6A6"/>
   </sheetPr>
@@ -11809,7 +11806,7 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -12121,14 +12118,14 @@
         <v>63</v>
       </c>
       <c r="C24" s="7" t="str">
-        <f>IF(SUM(C22:H22)=0,"⚠ Aún no hay dolores con casos.",IF(ABS(SUM(C22:H22)-1)&lt;0.0005,"✔ La atribución suma 100 %.","⚠ La atribución suma "&amp;FIXED(SUM(C22:H22)*100,1)&amp;" %; debe sumar 100 %. Revisa la fila 21."))</f>
+        <f>IF(SUM(C22:H22)=0,"⚠ Aún no hay dolores con casos.",IF(ABS(SUM(C22:H22)-1)&lt;0.0005,"✔ El impacto de los dolores suma 100 %.","⚠ El impacto de los dolores suma "&amp;FIXED(SUM(C22:H22)*100,1)&amp;" %; debe sumar 100 %. Revisa la fila 21."))</f>
         <v>⚠ Aún no hay dolores con casos.</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C25" s="11" t="str">
-        <f>"La suma de prevalencias es "&amp;FIXED(SUM(C19:H19)*100,0)&amp;" %. Puede pasar de 100 % porque un caso puede tener varios dolores. Es normal."</f>
-        <v>La suma de prevalencias es 0 %. Puede pasar de 100 % porque un caso puede tener varios dolores. Es normal.</v>
+        <f>"Los % dolor suman "&amp;FIXED(SUM(C19:H19)*100,0)&amp;" %. Puede pasar de 100 % porque un caso puede tener varios dolores. Es normal."</f>
+        <v>Los % dolor suman 0 %. Puede pasar de 100 % porque un caso puede tener varios dolores. Es normal.</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -12531,7 +12528,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B50" s="12" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="C50" s="34">
         <f t="shared" ref="C50:H50" si="11">C22</f>
@@ -12676,7 +12673,7 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B55" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C55" s="35" t="str">
         <f>IF(C17="","",IF(AND(C50&gt;Cobertura_Atrib_Min,C52&lt;Cobertura_Resuelto_Min),"⚠ SIN COBERTURA",IF(C52&gt;=Cobertura_Resuelto_Min,"✔ Cubierto","○ Peso bajo")))</f>
@@ -12708,19 +12705,19 @@
         <v>66</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>87</v>
@@ -12967,22 +12964,22 @@
     </row>
     <row r="67" spans="1:14" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C67" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="D67" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="E67" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="F67" s="37" t="s">
         <v>102</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C67" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="D67" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="E67" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="F67" s="37" t="s">
-        <v>101</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>87</v>
@@ -13222,7 +13219,7 @@
     </row>
     <row r="77" spans="1:14" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -13241,7 +13238,7 @@
     <row r="79" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4"/>
       <c r="B79" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C79" s="4" t="str">
         <f t="shared" ref="C79:H79" si="22">IF(C$17="","Dolor "&amp;(COLUMN()-2),C$17)</f>
@@ -13534,7 +13531,7 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B88" s="20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C88" s="30">
         <f t="shared" ref="C88:H88" si="24">PRODUCT(C80:C87)</f>
@@ -13563,7 +13560,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B89" s="20" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C89" s="30">
         <f t="shared" ref="C89:H89" si="25">1-C88</f>
@@ -13593,7 +13590,7 @@
     <row r="91" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="4"/>
       <c r="B91" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C91" s="4" t="str">
         <f t="shared" ref="C91:H91" si="26">IF(C$17="","Dolor "&amp;(COLUMN()-2),C$17)</f>
@@ -13886,7 +13883,7 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B100" s="20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C100" s="30">
         <f t="shared" ref="C100:H100" si="28">PRODUCT(C92:C99)</f>
@@ -13915,7 +13912,7 @@
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B101" s="20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C101" s="30">
         <f t="shared" ref="C101:H101" si="29">1-C100</f>
@@ -13945,7 +13942,7 @@
     <row r="103" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="4"/>
       <c r="B103" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C103" s="4" t="str">
         <f t="shared" ref="C103:H103" si="30">IF(C$17="","Dolor "&amp;(COLUMN()-2),C$17)</f>
@@ -13972,19 +13969,19 @@
         <v>Dolor 6</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L103" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M103" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
@@ -14413,13 +14410,13 @@
     </row>
     <row r="113" spans="1:3" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -14496,7 +14493,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B123" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>14</v>
@@ -14504,7 +14501,7 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B124" s="14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C124" s="16">
         <f>N(C8)</f>
@@ -14513,7 +14510,7 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B125" s="14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C125" s="16">
         <f>N(D44)</f>
@@ -14522,7 +14519,7 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B126" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C126" s="16">
         <f>N(C44)</f>
@@ -14540,7 +14537,7 @@
     </row>
     <row r="129" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B129" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>14</v>
@@ -14548,7 +14545,7 @@
     </row>
     <row r="130" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B130" s="14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C130" s="14" t="str">
         <f>IF(C7="%","pp",IF(C7="","puntos",C7))</f>
@@ -14557,7 +14554,7 @@
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B131" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C131" s="14">
         <f>IF(C10="",IF(C6="Sube es mejor",100,0),C10)</f>
@@ -14566,7 +14563,7 @@
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B132" s="14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C132" s="14">
         <f>IF(MAX(C22:H22)=0,0,MATCH(MAX(C22:H22),C22:H22,0))</f>
@@ -14575,7 +14572,7 @@
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B133" s="14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C133" s="14" t="str">
         <f>IF(C132=0,"",INDEX(C17:H17,C132))</f>
@@ -14661,17 +14658,17 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Casos" error="Escribe un número entero mayor o igual a 0." sqref="C13" xr:uid="{21BE1331-8345-44C0-B0E9-0892D5953017}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Casos" error="Escribe un número entero mayor o igual a 0." sqref="C13" xr:uid="{28771E3B-9EC1-41B3-BBAC-53F69121EC49}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Casos" error="Escribe un número entero mayor o igual a 0." sqref="C18:H18" xr:uid="{C41BF1BF-9674-4D75-8D7C-25B98860E3FC}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Casos" error="Escribe un número entero mayor o igual a 0." sqref="C18:H18" xr:uid="{F8D602B1-2864-4E9C-80BC-73623D18D2FE}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Porcentaje" error="Escribe un porcentaje entre 0 % y 100 % (ej. 40 %)." sqref="C21:H21" xr:uid="{0C1DB5EE-4905-4AB3-9B8C-42E03ED44B15}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Porcentaje" error="Escribe un porcentaje entre 0 % y 100 % (ej. 40 %)." sqref="C21:H21" xr:uid="{E7893D8E-A427-46C4-9E30-8038CA23F712}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Porcentaje" error="Escribe un porcentaje entre 0 % y 100 % (ej. 40 %)." sqref="C29:I36" xr:uid="{5E37C835-C579-4086-80AB-9CF61C2F5772}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Porcentaje" error="Escribe un porcentaje entre 0 % y 100 % (ej. 40 %)." sqref="C29:I36" xr:uid="{00D5BBBC-E95B-486D-8C31-738350543643}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -14681,13 +14678,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D9DBD36B-480D-4D74-94AD-091236B09A6B}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{20DCFD48-E539-4830-B380-4646AA85106D}">
           <x14:formula1>
             <xm:f>Parametros!$B$19:$B$20</xm:f>
           </x14:formula1>
           <xm:sqref>C6</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5628D8A2-F857-4C0C-8422-B3450077377A}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D2172F5E-6F63-4E7B-B182-6C4117B2E674}">
           <x14:formula1>
             <xm:f>Parametros!$C$19:$C$21</xm:f>
           </x14:formula1>
@@ -14700,7 +14697,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B05A9AF6-E901-4169-8B82-59B6556F13C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9BAF241-AA88-4720-9067-68764A80A482}">
   <sheetPr>
     <tabColor rgb="FFA6A6A6"/>
   </sheetPr>
